--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfried\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA7916D9-72EF-495C-8CCA-7A7BE2C5774C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
   <sheets>
     <sheet name="tir_fondos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
   <si>
     <t>fondo</t>
   </si>
@@ -113,6 +126,9 @@
   </si>
   <si>
     <t>Soja</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -596,9 +612,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -972,6 +989,43 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3BDEE73B-F8BB-4391-9788-605BBF507035}">
+  <we:reference id="wa200000565" version="1.0.0.80" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200000565" version="1.0.0.80" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>RDP.Data</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Price</we:customFunctionIds>
+        <we:customFunctionIds>RDP.HistoricalPricing</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Analytics</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Search</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Now</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Today</we:customFunctionIds>
+        <we:customFunctionIds>RDP.Aggregate</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24BE737-EAE7-45F7-815A-66ACF5C2EE77}">
   <dimension ref="A1:E24"/>
@@ -1005,10 +1059,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>7.4000000000000003E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>7.4000000000000003E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="E2">
         <v>0.04</v>
@@ -1022,13 +1076,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.8431E-2</v>
+        <v>3.7940136510393074E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.8800000000000001E-2</v>
+        <v>3.8300000000000001E-2</v>
       </c>
       <c r="E3">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,13 +1093,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.1067999999999997E-2</v>
+        <v>6.358910638721893E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.2E-2</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="E4">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1056,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>7.9712000000000005E-2</v>
+        <v>8.5665361461420897E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>8.1299999999999997E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="E5">
-        <v>3.9</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,13 +1127,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.6501999999999997E-2</v>
+        <v>5.5529128959256546E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.7299999999999997E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="E6">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1090,13 +1144,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>4.7143999999999998E-2</v>
+        <v>4.6362626711111687E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>4.7699999999999999E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="E7">
-        <v>1.1499999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1107,10 +1161,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.18609999999999999</v>
+        <v>0.192</v>
       </c>
       <c r="D8" s="1">
-        <v>0.204486</v>
+        <v>0.21160935225657296</v>
       </c>
       <c r="E8">
         <v>0.05</v>
@@ -1124,13 +1178,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.24390000000000001</v>
+        <v>0.24970000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.2707</v>
+        <v>0.27750000000000002</v>
       </c>
       <c r="E9">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1141,13 +1195,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.246729</v>
+        <v>0.2632839630851358</v>
       </c>
       <c r="D10" s="1">
-        <v>0.26700000000000002</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="E10">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1158,13 +1212,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.25786799999999999</v>
+        <v>0.27429068584860927</v>
       </c>
       <c r="D11" s="1">
-        <v>0.2853</v>
+        <v>0.307</v>
       </c>
       <c r="E11">
-        <v>0.21440000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,13 +1229,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>7.2999999999999995E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="E12">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1192,13 +1246,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>7.0499999999999993E-2</v>
+        <v>8.1799999999999998E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>6.9500000000000006E-2</v>
+        <v>8.0500000000000002E-2</v>
       </c>
       <c r="E13">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1209,10 +1263,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>0.27500000000000002</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.28499999999999998</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="E14">
         <v>0.78</v>
@@ -1226,13 +1280,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.301454</v>
+        <v>0.31239545716552247</v>
       </c>
       <c r="D15" s="1">
-        <v>0.29499999999999998</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="E15">
-        <v>1.1599999999999999</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1243,13 +1297,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.26700000000000002</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="D16" s="1">
-        <v>0.29149999999999998</v>
+        <v>0.317</v>
       </c>
       <c r="E16">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1260,13 +1314,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.22345400000000001</v>
+        <v>0.24154598347804559</v>
       </c>
       <c r="D17" s="1">
-        <v>0.240091</v>
-      </c>
-      <c r="E17">
-        <v>0.3483</v>
+        <v>0.26154674010542056</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.33240989128652831</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1277,13 +1331,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.29834699999999997</v>
+        <v>0.29076406467361915</v>
       </c>
       <c r="D18" s="1">
-        <v>0.3206</v>
+        <v>0.31190000000000001</v>
       </c>
       <c r="E18">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,29 +1348,56 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.31743900000000003</v>
+        <v>0.33715002196051197</v>
       </c>
       <c r="D19" s="1">
-        <v>0.29799999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="E19">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1326,10 +1407,10 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>4.9779999999999998E-2</v>
+        <v>4.9975609611002003E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.04E-2</v>
+        <v>5.0599999999999999E-2</v>
       </c>
       <c r="E23">
         <v>2.2799999999999998</v>
@@ -1339,8 +1420,337 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="cacb3d8f6664af26f6d55f537786b099">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de5b95b4a3c8595e9563ac81186c2058" ns2:_="" ns3:_="">
+    <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <xsd:import namespace="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="14def1a7-4a65-4794-a890-bf5d96e78463" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="23" nillable="true" ma:displayName="Sign-off status" ma:internalName="Sign_x002d_off_x0020_status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b80a8b0a-2819-4368-b347-46490e6c629e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{533d0a59-4079-4776-b0c6-0cef15366990}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b80a8b0a-2819-4368-b347-46490e6c629e">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAC21C5C-D4D1-4E8C-8737-D2FF0CFC7886}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{1123ebae-a006-42c7-9ea3-c84a2feb0e65}" enabled="0" method="" siteId="{1123ebae-a006-42c7-9ea3-c84a2feb0e65}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA7916D9-72EF-495C-8CCA-7A7BE2C5774C}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32BD5754-2514-4B64-91E1-6972C53B2C23}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -1062,10 +1062,10 @@
         <v>7.7999999999999996E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>7.7999999999999996E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E2">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1076,13 +1076,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.7940136510393074E-2</v>
+        <v>4.0294096447862415E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.8300000000000001E-2</v>
+        <v>4.07E-2</v>
       </c>
       <c r="E3">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1093,13 +1093,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.358910638721893E-2</v>
+        <v>6.3686022630380812E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4600000000000005E-2</v>
+        <v>6.4699999999999994E-2</v>
       </c>
       <c r="E4">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1110,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>8.5665361461420897E-2</v>
+        <v>9.150663398421921E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>8.7499999999999994E-2</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="E5">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1127,13 +1127,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.5529128959256546E-2</v>
+        <v>5.8154513150069587E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.6300000000000003E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="E6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1144,13 +1144,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>4.6362626711111687E-2</v>
+        <v>4.6948949045872101E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>4.6899999999999997E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="E7">
-        <v>1.1200000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,13 +1161,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.192</v>
+        <v>0.18073700000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21160935225657296</v>
+        <v>0.19804644414406303</v>
       </c>
       <c r="E8">
-        <v>0.05</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1178,10 +1178,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.24970000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="D9" s="1">
-        <v>0.27750000000000002</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="E9">
         <v>0.16</v>
@@ -1195,10 +1195,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.2632839630851358</v>
+        <v>0.27082370450735027</v>
       </c>
       <c r="D10" s="1">
-        <v>0.28799999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="E10">
         <v>0.31</v>
@@ -1229,13 +1229,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>6.2E-2</v>
+        <v>9.1399999999999995E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>6.2E-2</v>
+        <v>9.5699999999999993E-2</v>
       </c>
       <c r="E12">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1246,10 +1246,10 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>8.1799999999999998E-2</v>
+        <v>8.6699999999999999E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>8.0500000000000002E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="E13">
         <v>1.41</v>
@@ -1280,13 +1280,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.31239545716552247</v>
+        <v>0.315</v>
       </c>
       <c r="D15" s="1">
         <v>0.30299999999999999</v>
       </c>
       <c r="E15">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1297,13 +1297,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.28899999999999998</v>
+        <v>0.29139999999999999</v>
       </c>
       <c r="D16" s="1">
-        <v>0.317</v>
+        <v>0.31969999999999998</v>
       </c>
       <c r="E16">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1314,13 +1314,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.24154598347804559</v>
+        <v>0.24369514243083842</v>
       </c>
       <c r="D17" s="1">
-        <v>0.26154674010542056</v>
+        <v>0.26419134985763087</v>
       </c>
       <c r="E17" s="2">
-        <v>0.33240989128652831</v>
+        <v>0.32847424022503258</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1331,13 +1331,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.29076406467361915</v>
+        <v>0.29085137012421658</v>
       </c>
       <c r="D18" s="1">
-        <v>0.31190000000000001</v>
+        <v>0.312</v>
       </c>
       <c r="E18">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1348,13 +1348,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.33715002196051197</v>
+        <v>0.34395843761818251</v>
       </c>
       <c r="D19" s="1">
-        <v>0.312</v>
+        <v>0.317</v>
       </c>
       <c r="E19">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1448,17 +1448,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="cacb3d8f6664af26f6d55f537786b099">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de5b95b4a3c8595e9563ac81186c2058" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
     <xsd:import namespace="b80a8b0a-2819-4368-b347-46490e6c629e"/>
     <xsd:element name="properties">
@@ -1548,7 +1539,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="14def1a7-4a65-4794-a890-bf5d96e78463" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="14def1a7-4a65-4794-a890-bf5d96e78463" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1574,7 +1565,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b80a8b0a-2819-4368-b347-46490e6c629e" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1593,7 +1584,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1621,8 +1612,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1711,6 +1702,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
   <ds:schemaRefs>
@@ -1723,15 +1723,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAC21C5C-D4D1-4E8C-8737-D2FF0CFC7886}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1749,6 +1741,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1123ebae-a006-42c7-9ea3-c84a2feb0e65}" enabled="0" method="" siteId="{1123ebae-a006-42c7-9ea3-c84a2feb0e65}" removed="1"/>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32BD5754-2514-4B64-91E1-6972C53B2C23}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38FAD81A-75A5-4D35-995D-A451661AF891}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>fondo</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Latam Selection</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24BE737-EAE7-45F7-815A-66ACF5C2EE77}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -1059,13 +1062,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>7.7999999999999996E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>7.4000000000000003E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="E2">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1076,10 +1079,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>4.0294096447862415E-2</v>
+        <v>3.9313610016860512E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>4.07E-2</v>
+        <v>3.9699999999999999E-2</v>
       </c>
       <c r="E3">
         <v>0.71</v>
@@ -1093,13 +1096,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.3686022630380812E-2</v>
+        <v>6.3879841463645004E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4699999999999994E-2</v>
+        <v>6.4899999999999999E-2</v>
       </c>
       <c r="E4">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1110,13 +1113,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.150663398421921E-2</v>
+        <v>9.0741495259516913E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.3600000000000003E-2</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="E5">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1127,13 +1130,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.8154513150069587E-2</v>
+        <v>5.5918286313928256E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>5.67E-2</v>
       </c>
       <c r="E6">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1144,13 +1147,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>4.6948949045872101E-2</v>
+        <v>4.7828117787232838E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>4.7500000000000001E-2</v>
+        <v>4.8399999999999999E-2</v>
       </c>
       <c r="E7">
-        <v>1.1100000000000001</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,10 +1164,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.18073700000000001</v>
+        <v>0.192</v>
       </c>
       <c r="D8" s="1">
-        <v>0.19804644414406303</v>
+        <v>0.21160935225657296</v>
       </c>
       <c r="E8">
         <v>5.5E-2</v>
@@ -1178,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.254</v>
+        <v>0.24229999999999999</v>
       </c>
       <c r="D9" s="1">
-        <v>0.28299999999999997</v>
+        <v>0.26929999999999998</v>
       </c>
       <c r="E9">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1195,10 +1198,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.27082370450735027</v>
+        <v>0.26412350379638594</v>
       </c>
       <c r="D10" s="1">
-        <v>0.29699999999999999</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="E10">
         <v>0.31</v>
@@ -1212,13 +1215,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.27429068584860927</v>
+        <v>0.26512677031170012</v>
       </c>
       <c r="D11" s="1">
-        <v>0.307</v>
+        <v>0.29520000000000002</v>
       </c>
       <c r="E11">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1229,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>9.1399999999999995E-2</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>9.5699999999999993E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="E12">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1246,13 +1249,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>8.6699999999999999E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>8.5199999999999998E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="E13">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1263,13 +1266,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>0.29199999999999998</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.30099999999999999</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="E14">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,10 +1286,10 @@
         <v>0.315</v>
       </c>
       <c r="D15" s="1">
-        <v>0.30299999999999999</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="E15">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1297,13 +1300,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.29139999999999999</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="D16" s="1">
-        <v>0.31969999999999998</v>
+        <v>0.313</v>
       </c>
       <c r="E16">
-        <v>2.84</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1314,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.24369514243083842</v>
+        <v>0.22806018191709493</v>
       </c>
       <c r="D17" s="1">
-        <v>0.26419134985763087</v>
+        <v>0.24609713481414583</v>
       </c>
       <c r="E17" s="2">
-        <v>0.32847424022503258</v>
+        <v>0.32447791217453337</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1331,10 +1334,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.29085137012421658</v>
+        <v>0.2896287908741888</v>
       </c>
       <c r="D18" s="1">
-        <v>0.312</v>
+        <v>0.31059999999999999</v>
       </c>
       <c r="E18">
         <v>2.29</v>
@@ -1348,13 +1351,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.34395843761818251</v>
+        <v>0.34195801639844087</v>
       </c>
       <c r="D19" s="1">
-        <v>0.317</v>
+        <v>0.314</v>
       </c>
       <c r="E19">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1407,13 +1410,13 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>4.9975609611002003E-2</v>
+        <v>5.0073169425910891E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.0599999999999999E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="E23">
-        <v>2.2799999999999998</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1428,6 +1431,23 @@
       </c>
       <c r="E24" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.25339</v>
+      </c>
+      <c r="E25">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -1436,15 +1456,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1703,21 +1720,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
-    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1742,9 +1759,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
